--- a/Output/adf_weekly.xlsx
+++ b/Output/adf_weekly.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
